--- a/data/subsidiaries/sub_usd.xlsx
+++ b/data/subsidiaries/sub_usd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\00-CLaude-Plugins\fin-consol-auto-populate\data\subsidiaries\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_352D7A8F880E892A88C15622708E2C2DF6EC6A98" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9851FA9-9963-4214-AC99-57B9D063CD49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6255" yWindow="6945" windowWidth="13245" windowHeight="9045" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12705" yWindow="6345" windowWidth="13245" windowHeight="9045" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BS" sheetId="1" r:id="rId1"/>
@@ -564,6 +564,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -847,6 +851,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
